--- a/docs/02_機能毎のテスト/試験項目表_THLY.xlsx
+++ b/docs/02_機能毎のテスト/試験項目表_THLY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Git\home\issues\TSF4J5-4861_spring-func\docs\02_機能毎のテスト\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\git\spring-functionaltest\master\spring-functionaltest\docs\02_機能毎のテスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED42B87B-3D6A-45AC-AF30-8485E557C489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFA5751-4BCA-415D-9E29-713ADCBC2E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="18330" windowHeight="12165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大中項目" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="107">
   <si>
     <t>機能ID</t>
     <rPh sb="0" eb="2">
@@ -403,29 +403,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>th:includeの動作を確認する。</t>
-    <rPh sb="11" eb="13">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ｔｈ:includeを使用した画面を表示する。</t>
-    <rPh sb="11" eb="13">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>・フラグメントのHTMLが挿入されていること。
 ・th:replaceを設定した元のタグは削除されていること。</t>
     <rPh sb="13" eb="15">
@@ -450,14 +427,6 @@
     </rPh>
     <rPh sb="45" eb="46">
       <t>ノコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>フラグメントのコンテンツのみ挿入されていること。
-・th:includeを設定した元のタグが残っていること。</t>
-    <rPh sb="14" eb="16">
-      <t>ソウニュウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1290,11 +1259,6 @@
 ~{templatename} 
 ~{::selector}
 ~{this::selector}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>【フラグメントのパラメータの記法】
-th:replace="::frag (${value1},${value2})"</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1870,6 +1834,18 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1914,18 +1890,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1933,22 +1897,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <border>
         <left style="thin">
@@ -2333,15 +2282,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.25" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="9.734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.26171875" customWidth="1"/>
+    <col min="3" max="3" width="13.62890625" customWidth="1"/>
     <col min="4" max="4" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2352,19 +2301,19 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="52" cm="1">
+      <c r="C2" s="37" cm="1">
         <f t="array" aca="1" ref="C2" ca="1">SUMPRODUCT(IF(LEFT($A$5:$A$65494, 4)=$B$1, N(INDIRECT($A$5:$A$65494 &amp; "!C2")), 0))</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -2378,12 +2327,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27" x14ac:dyDescent="0.15">
-      <c r="A5" s="53" t="str">
+    <row r="5" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="38" t="str">
         <f>IF(B5="","",($B$1&amp;TEXT(IF(B5="","",COUNTA($B$5:B5)),"00")))</f>
         <v>THLY01</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="39" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="22" t="str">
@@ -2394,7 +2343,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="str">
         <f>IF(B6="","",($B$1&amp;TEXT(IF(B6="","",COUNTA($B$5:B6)),"00")))</f>
         <v>THLY02</v>
@@ -2410,8 +2359,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="55" t="str">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="40" t="str">
         <f>IF(B7="","",($B$1&amp;TEXT(IF(B7="","",COUNTA($B$5:B7)),"00")))</f>
         <v>THLY03</v>
       </c>
@@ -2429,7 +2378,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A5:B7">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>A5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2446,25 +2395,25 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="47.75" customWidth="1"/>
-    <col min="5" max="5" width="61.25" customWidth="1"/>
-    <col min="6" max="7" width="41.75" customWidth="1"/>
-    <col min="8" max="8" width="48.375" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="11.26171875" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="47.734375" customWidth="1"/>
+    <col min="5" max="5" width="61.26171875" customWidth="1"/>
+    <col min="6" max="7" width="41.734375" customWidth="1"/>
+    <col min="8" max="8" width="48.3671875" customWidth="1"/>
+    <col min="9" max="9" width="16.734375" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -2484,14 +2433,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="40" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="44">
-        <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
-        <v>5</v>
+      <c r="B2" s="45"/>
+      <c r="C2" s="48">
+        <f ca="1">COUNTIFS($B$9:$B$65494,"&lt;&gt;",$J$9:$J$65494,"&lt;&gt;論理削除")</f>
+        <v>4</v>
       </c>
       <c r="D2" s="17" t="str">
         <f>大中項目!B1</f>
@@ -2505,10 +2454,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="45"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>Thymeleafにおける画面レイアウト</v>
@@ -2521,7 +2470,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2532,33 +2481,33 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="46" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="48"/>
-    </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="49" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="52"/>
+    </row>
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="55"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -2569,7 +2518,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -2598,12 +2547,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="33">
-        <f t="shared" ref="B9:B13" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
+        <f t="shared" ref="B9:B12" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
@@ -2613,20 +2562,20 @@
         <v>37</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="24"/>
       <c r="B10" s="33">
         <f t="shared" ca="1" si="0"/>
@@ -2642,17 +2591,17 @@
         <v>39</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="24"/>
       <c r="B11" s="33">
         <f t="shared" ca="1" si="0"/>
@@ -2662,24 +2611,24 @@
         <v>24</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="24"/>
+    <row r="12" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
       <c r="B12" s="33">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
@@ -2688,56 +2637,30 @@
         <v>24</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>93</v>
-      </c>
       <c r="F12" s="12" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="15"/>
-      <c r="B13" s="33">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="37" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="37" t="s">
-        <v>53</v>
+    <row r="13" spans="1:9" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="41" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A14:XFD14"/>
+    <mergeCell ref="A13:XFD13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -2745,21 +2668,16 @@
     <mergeCell ref="A6:I6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A11:A13">
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>A11&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:B13">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>B9&lt;&gt;""</formula>
+  <conditionalFormatting sqref="A11:A12 B9:B12">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>A9&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:I13" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:I12" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Selenium:○,Seleniumu:△,Selenium:×,JUnit:○,JUnit:△,Junit:×,手動実行,机上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C13" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C12" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"正常,クライアントエラー,サーバーエラー"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2780,24 +2698,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="47.75" customWidth="1"/>
-    <col min="5" max="5" width="61.25" customWidth="1"/>
-    <col min="6" max="7" width="41.75" customWidth="1"/>
-    <col min="8" max="8" width="48.375" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="11.26171875" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="47.734375" customWidth="1"/>
+    <col min="5" max="5" width="61.26171875" customWidth="1"/>
+    <col min="6" max="7" width="41.734375" customWidth="1"/>
+    <col min="8" max="8" width="48.3671875" customWidth="1"/>
+    <col min="9" max="9" width="16.734375" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:10" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -2817,12 +2735,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="40" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="44">
+      <c r="B2" s="45"/>
+      <c r="C2" s="48">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>4</v>
       </c>
@@ -2838,10 +2756,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="45"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>Thymeleafにおける画面レイアウト</v>
@@ -2854,7 +2772,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2865,33 +2783,33 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="46" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="48"/>
-    </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="49" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="55"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -2902,7 +2820,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -2931,9 +2849,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="135" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" ht="129" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B9" s="16">
         <f t="shared" ref="B9:B12" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
@@ -2943,23 +2861,23 @@
         <v>24</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="148.5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" ht="141.9" x14ac:dyDescent="0.3">
       <c r="A10" s="24"/>
       <c r="B10" s="18">
         <f t="shared" ref="B10:B11" ca="1" si="1">IF(A10&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B10)-1,COLUMN(B10),4))+1)</f>
@@ -2972,20 +2890,20 @@
         <v>32</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="135" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" ht="129" x14ac:dyDescent="0.3">
       <c r="A11" s="24"/>
       <c r="B11" s="18">
         <f t="shared" ca="1" si="1"/>
@@ -2995,24 +2913,24 @@
         <v>24</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="25"/>
     </row>
-    <row r="12" spans="1:10" ht="175.5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" ht="167.7" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -3022,17 +2940,17 @@
         <v>24</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>25</v>
@@ -3083,24 +3001,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="47.75" customWidth="1"/>
-    <col min="5" max="5" width="61.25" customWidth="1"/>
-    <col min="6" max="7" width="41.75" customWidth="1"/>
-    <col min="8" max="8" width="48.375" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="11.26171875" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="47.734375" customWidth="1"/>
+    <col min="5" max="5" width="61.26171875" customWidth="1"/>
+    <col min="6" max="7" width="41.734375" customWidth="1"/>
+    <col min="8" max="8" width="48.3671875" customWidth="1"/>
+    <col min="9" max="9" width="16.734375" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -3120,12 +3038,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="40" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="44">
+      <c r="B2" s="45"/>
+      <c r="C2" s="48">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>1</v>
       </c>
@@ -3141,10 +3059,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="45"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>Thymeleafにおける画面レイアウト</v>
@@ -3157,7 +3075,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -3168,33 +3086,33 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="46" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="48"/>
-    </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="49" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="52"/>
+    </row>
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="55"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -3205,7 +3123,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -3234,9 +3152,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="125.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="125.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B9" s="18">
         <f t="shared" ref="B9" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
@@ -3249,12 +3167,12 @@
         <v>33</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
       <c r="H9" s="13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>25</v>
@@ -3296,114 +3214,114 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:E12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="67.375" customWidth="1"/>
-    <col min="4" max="4" width="60.75" customWidth="1"/>
-    <col min="5" max="5" width="37.875" customWidth="1"/>
+    <col min="3" max="3" width="67.3671875" customWidth="1"/>
+    <col min="4" max="4" width="60.734375" customWidth="1"/>
+    <col min="5" max="5" width="37.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C4" s="27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="2:5" ht="54" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:5" ht="51.6" x14ac:dyDescent="0.3">
       <c r="B12" s="34">
         <v>6</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3418,94 +3336,94 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:E10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="80.125" customWidth="1"/>
-    <col min="4" max="4" width="45.625" customWidth="1"/>
-    <col min="5" max="5" width="77.125" customWidth="1"/>
+    <col min="3" max="3" width="80.1015625" customWidth="1"/>
+    <col min="4" max="4" width="45.62890625" customWidth="1"/>
+    <col min="5" max="5" width="77.1015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C4" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" ht="27" x14ac:dyDescent="0.15">
-      <c r="B6" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>76</v>
-      </c>
       <c r="D6" s="30" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="54" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="51.6" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="54" x14ac:dyDescent="0.15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="51.6" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>2</v>
       </c>
       <c r="C8" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>83</v>
-      </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="2:5" ht="54" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:5" ht="51.6" x14ac:dyDescent="0.3">
       <c r="B9" s="34">
         <v>3</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="34">
         <v>4</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
